--- a/medford_konveksnye_datchiki_uzi.xlsx
+++ b/medford_konveksnye_datchiki_uzi.xlsx
@@ -2148,7 +2148,7 @@
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>Конвексные датчики УЗИ для оснащения клиник и медицинских учреждений. В каталоге представлены модели брендов SonoScape, Siemens, GE, Samsung, Mindray — всего 20 позиций.</t>
+          <t>Конвексные датчики УЗИ для оснащения клиник и медицинских учреждений. В каталоге представлены модели брендов SonoScape, Siemens, GE, Samsung, Mindray.</t>
         </is>
       </c>
       <c r="H4" s="3" t="inlineStr">

--- a/medford_konveksnye_datchiki_uzi.xlsx
+++ b/medford_konveksnye_datchiki_uzi.xlsx
@@ -941,7 +941,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H10"/>
+  <dimension ref="A1:H11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -1022,12 +1022,12 @@
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>Как выбрать конвексные датчики УЗИ для клиники?</t>
+          <t>Что такое конвексный датчик УЗИ?</t>
         </is>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>Выбор зависит от задач отделения, совместимости с оборудованием и ключевых характеристик (Количество элементов, Диапазон частот, МГц, Радиус кривизны, мм). Учитывайте бренд, гарантию, сервис и наличие РУ. Поможем сравнить модели и подобрать оптимальную.</t>
+          <t>Конвексный датчик — ультразвуковой датчик с выпуклой рабочей поверхностью. Такая форма даёт широкое поле обзора и хорошее проникновение ультразвука вглубь, поэтому его применяют для сканирования брюшной полости, малого таза и в акушерстве. Рабочие частоты обычно лежат в диапазоне около 2–7,5 МГц.</t>
         </is>
       </c>
       <c r="G4" s="3" t="inlineStr">
@@ -1060,12 +1060,12 @@
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>Нужно ли регистрационное удостоверение (РУ)?</t>
+          <t>Какие бывают виды датчиков УЗИ?</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>Да. Это медицинское изделие; для закупки в клинику с медицинской лицензией необходимо действующее регистрационное удостоверение Росздравнадзора. Проверяйте наличие РУ на конкретную модель.</t>
+          <t>Основные типы — конвексные (для глубокого сканирования брюшной полости и малого таза), линейные (для поверхностных структур и сосудов), секторные фазированные (для кардиологии) и внутриполостные (трансвагинальные, трансректальные). Тип датчика выбирают под вид исследования и анатомическую зону; в этой категории представлены конвексные датчики.</t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr">
@@ -1098,12 +1098,12 @@
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>Какие бренды представлены в каталоге?</t>
+          <t>Как выбрать конвексный датчик под свой аппарат?</t>
         </is>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>В каталоге представлены SonoScape, Siemens, GE, Samsung, Mindray. Подберём модель под ваши задачи, совместимость и бюджет.</t>
+          <t>Датчик подбирают под марку и серию УЗИ-сканера: совместимость определяется разъёмом и платформой. Датчик одного производителя, как правило, не подходит к аппарату другого. Сначала уточняют модель сканера, затем — нужный частотный диапазон и радиус кривизны под планируемые исследования.</t>
         </is>
       </c>
       <c r="G6" s="3" t="inlineStr">
@@ -1136,12 +1136,12 @@
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>Сколько стоит оборудование?</t>
+          <t>Чем отличается объёмный 3D/4D датчик?</t>
         </is>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>Цена указывается по запросу и зависит от модели, комплектации и условий поставки. Отправьте запрос — подготовим коммерческое предложение за 1 день.</t>
+          <t>Объёмный конвексный датчик (например, GE RAB6-RS или Samsung 3DC2-6) формирует трёхмерное изображение и применяется там, где нужна объёмная реконструкция, в частности в акушерстве. Обычный конвексный датчик даёт двумерную картинку. Объёмный вариант выбирают, когда это предусмотрено протоколом исследования.</t>
         </is>
       </c>
       <c r="G7" s="3" t="inlineStr">
@@ -1174,12 +1174,12 @@
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>Есть ли гарантия, сервис и обучение?</t>
+          <t>Что даёт монокристальный датчик?</t>
         </is>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>Да. Обеспечиваем доставку по России, монтаж и ввод в эксплуатацию, обучение персонала, гарантийное и постгарантийное обслуживание, поставку расходных материалов. Телефон: +7 (499) 495-48-21.</t>
+          <t>Монокристальные конвексные датчики, такие как Samsung CV1-8A или Mindray SD8-1s, обеспечивают расширенный частотный диапазон, что помогает сочетать глубину проникновения и детализацию в одном датчике. Целесообразность монокристального исполнения оценивают по задачам кабинета и совместимости с конкретной платформой сканера.</t>
         </is>
       </c>
       <c r="G8" s="3" t="inlineStr">
@@ -1212,12 +1212,12 @@
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>Что такое конвексный датчик УЗИ?</t>
+          <t>Как частота влияет на исследование?</t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>Зависит от модели и клинической задачи. Подберём вариант под ваши требования и ответим на вопрос при консультации — напишите или позвоните: +7 (499) 495-48-21.</t>
+          <t>Частота определяет баланс глубины и разрешения: низкие частоты проникают глубже и подходят для крупных пациентов и глубоких структур, высокие дают более детальное изображение поверхностных зон. Широкополосные конвексные датчики перекрывают несколько задач, поэтому диапазон согласуют с планируемыми видами исследований.</t>
         </is>
       </c>
       <c r="G9" s="3" t="inlineStr">
@@ -1250,12 +1250,12 @@
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>Какие существуют виды датчиков для УЗИ?</t>
+          <t>Нужна ли регистрация Росздравнадзора?</t>
         </is>
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t>Зависит от модели и клинической задачи. Подберём вариант под ваши требования и ответим на вопрос при консультации — напишите или позвоните: +7 (499) 495-48-21.</t>
+          <t>УЗИ-датчик, применяемый в клинике, должен быть зарегистрированным медицинским изделием или входить в состав зарегистрированного комплекса. Статус регистрационного удостоверения уточняют до покупки. Это условие законной эксплуатации и один из критериев при подборе оригинального или совместимого датчика.</t>
         </is>
       </c>
       <c r="G10" s="3" t="inlineStr">
@@ -1264,6 +1264,44 @@
         </is>
       </c>
       <c r="H10" s="3" t="inlineStr">
+        <is>
+          <t>FAQ</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="n">
+        <v>22</v>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>FAQ_08</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="D11" s="3" t="n">
+        <v>180</v>
+      </c>
+      <c r="E11" s="3" t="inlineStr">
+        <is>
+          <t>Как продлить срок службы датчика?</t>
+        </is>
+      </c>
+      <c r="F11" s="3" t="inlineStr">
+        <is>
+          <t>Датчик — уязвимый элемент: чаще всего повреждаются линза, кабель и разъём. Ресурс продлевают аккуратное обращение, использование геля и обработка по инструкции, хранение в держателе без перегибов кабеля. Регулярная проверка целостности и своевременный ремонт помогают избежать полной замены дорогостоящего датчика.</t>
+        </is>
+      </c>
+      <c r="G11" s="3" t="inlineStr">
+        <is>
+          <t>konveksnye_datchiki_uzi</t>
+        </is>
+      </c>
+      <c r="H11" s="3" t="inlineStr">
         <is>
           <t>FAQ</t>
         </is>
@@ -2148,7 +2186,7 @@
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>Конвексные датчики УЗИ для оснащения клиник и медицинских учреждений. В каталоге представлены модели брендов SonoScape, Siemens, GE, Samsung, Mindray.</t>
+          <t>Конвексные датчики УЗИ — датчики с выпуклой рабочей поверхностью для глубокого сканирования брюшной полости, малого таза и акушерских исследований. В категории представлены модели SonoScape, Siemens, GE, Samsung, Mindray и SIUI. Диапазон частот линейки — от 1,0 до 8,4 МГц, число элементов — 128 или 192, радиус кривизны — от 20 мм у SIUI C3IN до 60 мм у Mindray SC6-1U. Отдельную группу составляют объёмные 3D/4D и монокристальные датчики, например GE RAB6-RS и Samsung CV1-8A.</t>
         </is>
       </c>
       <c r="H4" s="3" t="inlineStr">
@@ -2432,7 +2470,7 @@
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>Сравнение моделей по характеристикам</t>
+          <t>Типы датчиков УЗИ</t>
         </is>
       </c>
       <c r="F6" s="3" t="inlineStr"/>
@@ -2720,7 +2758,7 @@
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t>Что такое конвексные датчики УЗИ</t>
+          <t>Коротко о категории</t>
         </is>
       </c>
       <c r="F14" s="3" t="inlineStr"/>
@@ -4474,215 +4512,109 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E9"/>
+  <dimension ref="A1:C7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="34" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>04_COMPARE_ROWS — Сравнение моделей по характеристикам</t>
+          <t>04_COMPARE_ROWS — Типы датчиков УЗИ</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Модель</t>
+          <t>Тип датчика</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Бренд</t>
+          <t>Форма поля</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>Количество элементов</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>Диапазон частот, МГц</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>Радиус кривизны, мм</t>
+          <t>Основное применение</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>Конвексный широкополосный датчик SonoScape 3C-A</t>
+          <t>Конвексный</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>SonoScape</t>
+          <t>сектор с широким полем</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>128</t>
-        </is>
-      </c>
-      <c r="D4" s="3" t="inlineStr">
-        <is>
-          <t>1,0-6,0</t>
-        </is>
-      </c>
-      <c r="E4" s="3" t="inlineStr">
-        <is>
-          <t>50</t>
+          <t>брюшная полость, малый таз, акушерство</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>Siemens 6C2 конвексный датчик УЗИ</t>
+          <t>Линейный</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>Siemens</t>
+          <t>прямоугольник</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>128</t>
-        </is>
-      </c>
-      <c r="D5" s="3" t="inlineStr">
-        <is>
-          <t>2-6</t>
-        </is>
-      </c>
-      <c r="E5" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
+          <t>поверхностные структуры, сосуды</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>Объемный конвексный 3D/4D датчик GE RAB6-RS</t>
+          <t>Секторный (фазированный)</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>GE</t>
+          <t>узкий сектор</t>
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>192</t>
-        </is>
-      </c>
-      <c r="D6" s="3" t="inlineStr">
-        <is>
-          <t>2-8</t>
-        </is>
-      </c>
-      <c r="E6" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
+          <t>кардиология</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>Объемный конвексный датчик Samsung VN4-8</t>
+          <t>Внутриполостной</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>Samsung</t>
+          <t>конвекс малого радиуса</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>128</t>
-        </is>
-      </c>
-      <c r="D7" s="3" t="inlineStr">
-        <is>
-          <t>4-8</t>
-        </is>
-      </c>
-      <c r="E7" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="3" t="inlineStr">
-        <is>
-          <t>Объемный конвексный датчик Samsung CV1-8AD</t>
-        </is>
-      </c>
-      <c r="B8" s="3" t="inlineStr">
-        <is>
-          <t>Samsung</t>
-        </is>
-      </c>
-      <c r="C8" s="3" t="inlineStr">
-        <is>
-          <t>192</t>
-        </is>
-      </c>
-      <c r="D8" s="3" t="inlineStr">
-        <is>
-          <t>1-8</t>
-        </is>
-      </c>
-      <c r="E8" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="3" t="inlineStr">
-        <is>
-          <t>Siemens 6C1 HD конвексный датчик</t>
-        </is>
-      </c>
-      <c r="B9" s="3" t="inlineStr">
-        <is>
-          <t>Siemens</t>
-        </is>
-      </c>
-      <c r="C9" s="3" t="inlineStr">
-        <is>
-          <t>192</t>
-        </is>
-      </c>
-      <c r="D9" s="3" t="inlineStr">
-        <is>
-          <t>1,5-6,0</t>
-        </is>
-      </c>
-      <c r="E9" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
+          <t>трансвагинальные и трансректальные исследования</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A1:C1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -4694,7 +4626,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M24"/>
+  <dimension ref="A1:M25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -5020,12 +4952,12 @@
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>Тип и назначение</t>
+          <t>Уточните модель сканера</t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>Определите задачи, под которые подбирается конвексные датчики УЗИ: профиль отделения, поток и характер исследований или процедур.</t>
+          <t>Совместимость конвексного датчика определяется маркой и серией УЗИ-аппарата и типом разъёма. Прежде всего выясняют производителя и модель сканера, к которому подбирается датчик. Датчик Mindray рассчитан на платформы Mindray, GE — на GE и так далее; кросс-совместимость между брендами, как правило, отсутствует.</t>
         </is>
       </c>
       <c r="G9" s="3" t="inlineStr"/>
@@ -5065,12 +4997,12 @@
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>Совместимость с оборудованием</t>
+          <t>Определите вид исследований</t>
         </is>
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t>Проверьте совместимость с имеющейся техникой, платформой и разъёмами — это исключит лишние затраты на дооснащение.</t>
+          <t>Уточняют, какие исследования будут основными: абдоминальные, акушерско-гинекологические, урологические или педиатрические. От этого зависят частотный диапазон и радиус кривизны. Для глубоких абдоминальных задач берут более низкие частоты, для поверхностных и педиатрических — более высокие; конкретику определяет протокол кабинета.</t>
         </is>
       </c>
       <c r="G10" s="3" t="inlineStr"/>
@@ -5110,12 +5042,12 @@
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>Ключевые характеристики</t>
+          <t>Сверьте диапазон частот</t>
         </is>
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t>Сравните ключевые параметры моделей: Количество элементов, Диапазон частот, МГц, Радиус кривизны, мм. Значения — в таблице сравнения и карточках товаров.</t>
+          <t>Частота задаёт баланс глубины и разрешения: низкие частоты проникают глубже, высокие дают детализацию поверхностных структур. В линейке диапазоны от 1,0–6,0 МГц (SonoScape 3C-A) до 1,8–8,2 МГц (Mindray SD8-1s). Широкополосный датчик перекрывает больше задач; диапазон согласуют с планируемыми исследованиями.</t>
         </is>
       </c>
       <c r="G11" s="3" t="inlineStr"/>
@@ -5155,12 +5087,12 @@
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t>Бренд и качество</t>
+          <t>Оцените радиус кривизны и число элементов</t>
         </is>
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
-          <t>Выбор бренда влияет на ресурс, сервис и совместимость. В каталоге: SonoScape, Siemens, GE, Samsung, Mindray.</t>
+          <t>Радиус кривизны влияет на поле обзора и подход к анатомии: в линейке от 20 мм (SIUI C3IN) до 60 мм (Mindray SC6-1U). Число элементов (128 или 192) связано с плотностью линий и качеством картинки. Эти параметры подбирают под зону сканирования и требования к изображению.</t>
         </is>
       </c>
       <c r="G12" s="3" t="inlineStr"/>
@@ -5200,12 +5132,12 @@
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t>Регистрация и допуск</t>
+          <t>Решите про 3D/4D и монокристалл</t>
         </is>
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
-          <t>Для клиники с медицинской лицензией необходимо действующее регистрационное удостоверение (РУ) Росздравнадзора на модель.</t>
+          <t>Объёмные датчики (GE RAB6-RS, Samsung 3DC2-6) формируют 3D/4D изображение, а монокристальные (Samsung CV1-8A, Mindray SD8-1s) дают расширенный частотный диапазон. Эти опции берут, когда они действительно нужны протоколу — например, в акушерстве. Без такой задачи достаточно стандартного конвексного датчика.</t>
         </is>
       </c>
       <c r="G13" s="3" t="inlineStr"/>
@@ -5245,12 +5177,12 @@
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t>Гарантия и сервис</t>
+          <t>Проверьте состояние и регистрацию</t>
         </is>
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
-          <t>Уточняйте гарантию, наличие сервисной поддержки и поставку расходных материалов до закупки.</t>
+          <t>Датчик — уязвимый и дорогой элемент сканера, поэтому проверяют целостность линзы, кабеля и разъёма, отсутствие выпавших элементов. Для клинического применения нужен зарегистрированный медицинский изделие. Заранее уточняют гарантию и условия сервиса, включая ремонт датчиков и доступность совместимых моделей.</t>
         </is>
       </c>
       <c r="G14" s="3" t="inlineStr"/>
@@ -5300,7 +5232,7 @@
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t>Конвексные датчики УЗИ подбирают под задачи отделения и совместимость с имеющимся оборудованием. В нашем каталоге представлены SonoScape, Siemens, GE, Samsung, Mindray. При выборе обращают внимание на количество элементов, диапазон частот, радиус кривизны, а также на наличие регистрационного удостоверения и условия сервиса. Поможем сравнить модели и подобрать оптимальную под ваш поток исследований и бюджет.</t>
+          <t>Конвексный датчик выбирают в первую очередь под свой сканер: датчик, не совместимый с платформой по разъёму и серии, работать не будет, каким бы удачным ни был сам по себе. Дальше смотрят на диапазон частот и радиус кривизны под нужную глубину и зону, а также на число элементов. Объёмные 3D/4D и монокристальные датчики оправданы там, где это действительно требуется протоколом исследования.</t>
         </is>
       </c>
       <c r="H15" s="3" t="inlineStr">
@@ -5584,13 +5516,13 @@
       </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
-          <t>Что такое конвексные датчики УЗИ</t>
+          <t>Коротко о категории</t>
         </is>
       </c>
       <c r="F21" s="3" t="inlineStr"/>
       <c r="G21" s="3" t="inlineStr">
         <is>
-          <t>Конвексные датчики УЗИ — медицинское оборудование для оснащения клиник и медицинских учреждений. В каталоге Medford представлены модели брендов SonoScape, Siemens, GE, Samsung, Mindray. Подберём вариант под задачи вашего отделения.</t>
+          <t>Конвексный датчик УЗИ — датчик с выпуклой поверхностью, дающий широкое поле обзора и глубокое проникновение ультразвука, поэтому его применяют для брюшной полости, малого таза и акушерства. Рабочие частоты обычно 2–7,5 МГц; в линейке — от 1,0 до 8,4 МГц. Датчик подбирают под конкретную марку и серию УЗИ-сканера: совместимость определяется разъёмом и платформой. Ключевые параметры — диапазон частот, число элементов (128 или 192), радиус кривизны и наличие объёмного 3D/4D или монокристального исполнения.</t>
         </is>
       </c>
       <c r="H21" s="3" t="inlineStr">
@@ -5627,13 +5559,13 @@
       </c>
       <c r="E22" s="3" t="inlineStr">
         <is>
-          <t>Как выбрать и на что смотреть</t>
+          <t>Конвексные датчики: назначение</t>
         </is>
       </c>
       <c r="F22" s="3" t="inlineStr"/>
       <c r="G22" s="3" t="inlineStr">
         <is>
-          <t>При выборе оценивают назначение и совместимость с имеющимся оборудованием, ключевые характеристики (Количество элементов, Диапазон частот, МГц, Радиус кривизны, мм), бренд, наличие РУ, гарантию и сервис.</t>
+          <t>Конвексный датчик УЗИ имеет выпуклую рабочую поверхность, которая даёт широкое поле обзора и глубокое проникновение ультразвука. Благодаря этому его применяют для сканирования брюшной полости, малого таза, а также в акушерстве, гинекологии и урологии. Рабочие частоты обычно находятся в диапазоне около 2–7,5 МГц и подбираются под глубину исследования.</t>
         </is>
       </c>
       <c r="H22" s="3" t="inlineStr">
@@ -5670,13 +5602,13 @@
       </c>
       <c r="E23" s="3" t="inlineStr">
         <is>
-          <t>Оснащение и совместимость</t>
+          <t>Типы датчиков и их роль</t>
         </is>
       </c>
       <c r="F23" s="3" t="inlineStr"/>
       <c r="G23" s="3" t="inlineStr">
         <is>
-          <t>Уточняйте комплектацию, совместимость с вашей техникой и наличие расходных материалов. Специалисты Medford помогут собрать рабочее решение под ваш профиль.</t>
+          <t>Датчики УЗИ делятся на конвексные, линейные, секторные фазированные и внутриполостные. Конвексные отвечают за глубокое сканирование крупных областей, линейные — за поверхностные структуры и сосуды, секторные — за кардиологию, внутриполостные — за трансвагинальные и трансректальные исследования. Для полноценной работы кабинета обычно нужен набор датчиков под разные задачи.</t>
         </is>
       </c>
       <c r="H23" s="3" t="inlineStr">
@@ -5713,13 +5645,13 @@
       </c>
       <c r="E24" s="3" t="inlineStr">
         <is>
-          <t>Оплата и доставка</t>
+          <t>Ключевые характеристики</t>
         </is>
       </c>
       <c r="F24" s="3" t="inlineStr"/>
       <c r="G24" s="3" t="inlineStr">
         <is>
-          <t>Оплата — по счёту для юридических лиц и ИП. Доставка по всей России, монтаж и ввод в эксплуатацию. Гарантийное и постгарантийное обслуживание, обучение персонала. Телефон для консультаций: +7 (499) 495-48-21.</t>
+          <t>При выборе конвексного датчика сравнивают диапазон частот (в линейке от 1,0 до 8,4 МГц), число элементов (128 или 192), радиус кривизны (от 20 до 60 мм) и наличие объёмного 3D/4D или монокристального исполнения. Эти параметры определяют глубину, поле обзора и качество изображения, поэтому их согласуют с видами исследований.</t>
         </is>
       </c>
       <c r="H24" s="3" t="inlineStr">
@@ -5736,6 +5668,49 @@
       <c r="K24" s="3" t="inlineStr"/>
       <c r="L24" s="3" t="inlineStr"/>
       <c r="M24" s="3" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="3" t="n">
+        <v>21</v>
+      </c>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>SEO_05</t>
+        </is>
+      </c>
+      <c r="C25" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="D25" s="3" t="n">
+        <v>550</v>
+      </c>
+      <c r="E25" s="3" t="inlineStr">
+        <is>
+          <t>Совместимость и бренды</t>
+        </is>
+      </c>
+      <c r="F25" s="3" t="inlineStr"/>
+      <c r="G25" s="3" t="inlineStr">
+        <is>
+          <t>В категории представлены датчики SonoScape, Siemens, GE, Samsung, Mindray и SIUI. Датчик подбирают строго под марку и серию УЗИ-сканера: совместимость определяется разъёмом и платформой, а кросс-совместимость между брендами обычно отсутствует. Модель сканера уточняют до заказа, чтобы датчик корректно работал с аппаратом.</t>
+        </is>
+      </c>
+      <c r="H25" s="3" t="inlineStr">
+        <is>
+          <t>konveksnye_datchiki_uzi</t>
+        </is>
+      </c>
+      <c r="I25" s="3" t="inlineStr">
+        <is>
+          <t>SEO</t>
+        </is>
+      </c>
+      <c r="J25" s="3" t="inlineStr"/>
+      <c r="K25" s="3" t="inlineStr"/>
+      <c r="L25" s="3" t="inlineStr"/>
+      <c r="M25" s="3" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="1">
